--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/53.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/53.xlsx
@@ -426,13 +426,13 @@
         <v>-22.54093371306233</v>
       </c>
       <c r="E2">
-        <v>-14.37310234013885</v>
+        <v>-17.64435422295572</v>
       </c>
       <c r="F2">
-        <v>-0.05817887504832543</v>
+        <v>-0.02281172878580054</v>
       </c>
       <c r="G2">
-        <v>-14.63963906715408</v>
+        <v>-16.54902269129305</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.36536932718784</v>
       </c>
       <c r="E3">
-        <v>-15.39082706014868</v>
+        <v>-17.62442893732197</v>
       </c>
       <c r="F3">
-        <v>-0.3603192582802227</v>
+        <v>-0.2480961843859597</v>
       </c>
       <c r="G3">
-        <v>-14.77366815858425</v>
+        <v>-16.40642590800726</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.12539993004785</v>
       </c>
       <c r="E4">
-        <v>-13.97576497375784</v>
+        <v>-17.46507193699205</v>
       </c>
       <c r="F4">
-        <v>-0.7161908647273071</v>
+        <v>-0.1008638189471812</v>
       </c>
       <c r="G4">
-        <v>-13.985720248964</v>
+        <v>-15.89156655519426</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.80585632870266</v>
       </c>
       <c r="E5">
-        <v>-17.18033960528576</v>
+        <v>-18.97869173168582</v>
       </c>
       <c r="F5">
-        <v>-0.4175321096893762</v>
+        <v>0.3425736772824362</v>
       </c>
       <c r="G5">
-        <v>-14.13022887229873</v>
+        <v>-16.89649424054942</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.41827261578707</v>
       </c>
       <c r="E6">
-        <v>-16.09215635819059</v>
+        <v>-20.02524018875447</v>
       </c>
       <c r="F6">
-        <v>-0.5452257731983228</v>
+        <v>-0.03953729501572536</v>
       </c>
       <c r="G6">
-        <v>-12.21875794919725</v>
+        <v>-15.03578722274712</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.97015483239839</v>
       </c>
       <c r="E7">
-        <v>-17.32281445451509</v>
+        <v>-19.15007183050611</v>
       </c>
       <c r="F7">
-        <v>-0.5136434375991888</v>
+        <v>0.03911453314528211</v>
       </c>
       <c r="G7">
-        <v>-12.53504747001922</v>
+        <v>-14.87728161287236</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.46100566180688</v>
       </c>
       <c r="E8">
-        <v>-17.98715970533636</v>
+        <v>-19.22946050833458</v>
       </c>
       <c r="F8">
-        <v>-0.4841021992805528</v>
+        <v>0.1012155805983554</v>
       </c>
       <c r="G8">
-        <v>-11.78938019275378</v>
+        <v>-15.32008363147757</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.89096939643711</v>
       </c>
       <c r="E9">
-        <v>-16.56803557776064</v>
+        <v>-20.50740040177316</v>
       </c>
       <c r="F9">
-        <v>-0.2909774513592789</v>
+        <v>0.3013168387860068</v>
       </c>
       <c r="G9">
-        <v>-11.44921832804812</v>
+        <v>-14.50892052126319</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.3031432739317</v>
       </c>
       <c r="E10">
-        <v>-17.31053776148029</v>
+        <v>-20.96719901014197</v>
       </c>
       <c r="F10">
-        <v>-0.1107951157393444</v>
+        <v>0.5944478981450567</v>
       </c>
       <c r="G10">
-        <v>-10.56619982690386</v>
+        <v>-13.8459473610232</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.72865137162223</v>
       </c>
       <c r="E11">
-        <v>-19.33203497308232</v>
+        <v>-21.77530972528475</v>
       </c>
       <c r="F11">
-        <v>-0.07377371977342892</v>
+        <v>0.671265720876266</v>
       </c>
       <c r="G11">
-        <v>-9.652151582420004</v>
+        <v>-13.60405241955974</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.19083811456094</v>
       </c>
       <c r="E12">
-        <v>-18.58935617887636</v>
+        <v>-22.1327557641322</v>
       </c>
       <c r="F12">
-        <v>0.5758435946455825</v>
+        <v>0.7198138492521367</v>
       </c>
       <c r="G12">
-        <v>-9.343072429782566</v>
+        <v>-13.01428866337519</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-17.71048681427741</v>
       </c>
       <c r="E13">
-        <v>-19.94256836727045</v>
+        <v>-23.02223862871881</v>
       </c>
       <c r="F13">
-        <v>0.8984993249752125</v>
+        <v>1.0626005642046</v>
       </c>
       <c r="G13">
-        <v>-9.661901139033157</v>
+        <v>-12.15243447986349</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-17.34243596088366</v>
       </c>
       <c r="E14">
-        <v>-20.64087264467524</v>
+        <v>-22.57913197554227</v>
       </c>
       <c r="F14">
-        <v>0.6419928735961371</v>
+        <v>1.448931240052622</v>
       </c>
       <c r="G14">
-        <v>-9.795915333008395</v>
+        <v>-11.77558183894609</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-17.11128553236994</v>
       </c>
       <c r="E15">
-        <v>-22.3379182790497</v>
+        <v>-23.49229423071499</v>
       </c>
       <c r="F15">
-        <v>1.378327829577215</v>
+        <v>1.729230888342308</v>
       </c>
       <c r="G15">
-        <v>-8.836267634266619</v>
+        <v>-10.92464583462291</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-17.01660691754448</v>
       </c>
       <c r="E16">
-        <v>-22.55585561914285</v>
+        <v>-24.40193786158375</v>
       </c>
       <c r="F16">
-        <v>1.163762448169281</v>
+        <v>1.966606194553729</v>
       </c>
       <c r="G16">
-        <v>-8.645709322480631</v>
+        <v>-11.0067109479959</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-17.05283532044388</v>
       </c>
       <c r="E17">
-        <v>-22.57958935141705</v>
+        <v>-25.39524504974422</v>
       </c>
       <c r="F17">
-        <v>2.094045549270016</v>
+        <v>1.875426137792781</v>
       </c>
       <c r="G17">
-        <v>-8.045146566746984</v>
+        <v>-10.54720722714506</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.22826167407476</v>
       </c>
       <c r="E18">
-        <v>-24.2265636486887</v>
+        <v>-25.42117962038615</v>
       </c>
       <c r="F18">
-        <v>2.055852841796542</v>
+        <v>2.106590345218011</v>
       </c>
       <c r="G18">
-        <v>-8.381305981895659</v>
+        <v>-9.826246551239198</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.52170707274146</v>
       </c>
       <c r="E19">
-        <v>-25.67671688016498</v>
+        <v>-27.25103181198357</v>
       </c>
       <c r="F19">
-        <v>2.295557517144635</v>
+        <v>2.776048715668876</v>
       </c>
       <c r="G19">
-        <v>-7.736640138487841</v>
+        <v>-10.05463777744798</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.88899177983154</v>
       </c>
       <c r="E20">
-        <v>-25.59589720455009</v>
+        <v>-27.7922614399583</v>
       </c>
       <c r="F20">
-        <v>2.061522188301301</v>
+        <v>2.910991422319722</v>
       </c>
       <c r="G20">
-        <v>-8.355702222694935</v>
+        <v>-10.58075960618557</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-18.30076710052882</v>
       </c>
       <c r="E21">
-        <v>-28.29789273375874</v>
+        <v>-27.58938127594066</v>
       </c>
       <c r="F21">
-        <v>2.445662660736322</v>
+        <v>2.910015605519224</v>
       </c>
       <c r="G21">
-        <v>-7.548743505315427</v>
+        <v>-9.787794564800562</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-18.73946439272735</v>
       </c>
       <c r="E22">
-        <v>-27.37233604522703</v>
+        <v>-29.35457591565656</v>
       </c>
       <c r="F22">
-        <v>2.691354775671849</v>
+        <v>3.236292958133893</v>
       </c>
       <c r="G22">
-        <v>-7.472475157181697</v>
+        <v>-9.551686456939741</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-19.17196673308361</v>
       </c>
       <c r="E23">
-        <v>-29.53258570042408</v>
+        <v>-29.47207849497059</v>
       </c>
       <c r="F23">
-        <v>2.858100163650973</v>
+        <v>3.604225593965738</v>
       </c>
       <c r="G23">
-        <v>-6.640962123537414</v>
+        <v>-10.71941187446133</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-19.54935083808398</v>
       </c>
       <c r="E24">
-        <v>-28.06095844520343</v>
+        <v>-30.21791363555989</v>
       </c>
       <c r="F24">
-        <v>2.823315359672617</v>
+        <v>2.880462770056949</v>
       </c>
       <c r="G24">
-        <v>-7.759386896888174</v>
+        <v>-9.205943012454876</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-19.85266320084994</v>
       </c>
       <c r="E25">
-        <v>-29.28253242266853</v>
+        <v>-28.6340911725622</v>
       </c>
       <c r="F25">
-        <v>2.727817852008278</v>
+        <v>3.639253937960518</v>
       </c>
       <c r="G25">
-        <v>-7.262447527079255</v>
+        <v>-9.69736039230429</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-20.07126541982636</v>
       </c>
       <c r="E26">
-        <v>-28.30372993675463</v>
+        <v>-30.60872094242184</v>
       </c>
       <c r="F26">
-        <v>3.107669038031603</v>
+        <v>3.680410544001209</v>
       </c>
       <c r="G26">
-        <v>-8.563683935654108</v>
+        <v>-10.11697203940691</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-20.18940858315042</v>
       </c>
       <c r="E27">
-        <v>-28.6555199115665</v>
+        <v>-29.79922677846971</v>
       </c>
       <c r="F27">
-        <v>2.807650932085678</v>
+        <v>3.025690486380952</v>
       </c>
       <c r="G27">
-        <v>-7.647007118012074</v>
+        <v>-10.28239668945876</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-20.18160654158981</v>
       </c>
       <c r="E28">
-        <v>-29.58568432240101</v>
+        <v>-30.13962084844128</v>
       </c>
       <c r="F28">
-        <v>2.301899497980468</v>
+        <v>2.949593343290179</v>
       </c>
       <c r="G28">
-        <v>-7.091911394714778</v>
+        <v>-9.596488069722698</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-20.06066695743518</v>
       </c>
       <c r="E29">
-        <v>-28.74949933264768</v>
+        <v>-29.53316760933406</v>
       </c>
       <c r="F29">
-        <v>2.237961131627985</v>
+        <v>2.726505718042244</v>
       </c>
       <c r="G29">
-        <v>-8.369805146692231</v>
+        <v>-10.06029218922905</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-19.84297374430861</v>
       </c>
       <c r="E30">
-        <v>-28.14676849917477</v>
+        <v>-29.75106872163514</v>
       </c>
       <c r="F30">
-        <v>2.456436407177132</v>
+        <v>2.904150764307404</v>
       </c>
       <c r="G30">
-        <v>-6.418020055286275</v>
+        <v>-9.005251120773178</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-19.54133144944744</v>
       </c>
       <c r="E31">
-        <v>-27.65177006234434</v>
+        <v>-29.76802332831986</v>
       </c>
       <c r="F31">
-        <v>1.979480680728039</v>
+        <v>2.487485274168863</v>
       </c>
       <c r="G31">
-        <v>-7.948693822460318</v>
+        <v>-8.220840529061645</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-19.15818762577376</v>
       </c>
       <c r="E32">
-        <v>-27.97778849157855</v>
+        <v>-29.51598431471196</v>
       </c>
       <c r="F32">
-        <v>2.029187695100426</v>
+        <v>2.352088622181284</v>
       </c>
       <c r="G32">
-        <v>-6.425640931117677</v>
+        <v>-9.132621049851098</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-18.72948736428254</v>
       </c>
       <c r="E33">
-        <v>-27.77493096993095</v>
+        <v>-28.52681162332049</v>
       </c>
       <c r="F33">
-        <v>2.033520056617067</v>
+        <v>2.317384998208401</v>
       </c>
       <c r="G33">
-        <v>-6.491679693535058</v>
+        <v>-8.607489074229745</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-18.28504220577318</v>
       </c>
       <c r="E34">
-        <v>-27.26214468719839</v>
+        <v>-28.04388609819451</v>
       </c>
       <c r="F34">
-        <v>2.071686256333651</v>
+        <v>2.171241107536902</v>
       </c>
       <c r="G34">
-        <v>-7.452337108666311</v>
+        <v>-8.967388411440533</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-17.84347713757168</v>
       </c>
       <c r="E35">
-        <v>-26.7844087932852</v>
+        <v>-28.11788589195385</v>
       </c>
       <c r="F35">
-        <v>0.9404114020872562</v>
+        <v>2.317197787175369</v>
       </c>
       <c r="G35">
-        <v>-5.757589394020447</v>
+        <v>-8.829298935906454</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-17.40843867772126</v>
       </c>
       <c r="E36">
-        <v>-24.93058738876518</v>
+        <v>-28.42157441585624</v>
       </c>
       <c r="F36">
-        <v>2.117645736575774</v>
+        <v>2.291592950754836</v>
       </c>
       <c r="G36">
-        <v>-6.721835440516269</v>
+        <v>-8.521769118581396</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-17.01209412619713</v>
       </c>
       <c r="E37">
-        <v>-25.18715261214376</v>
+        <v>-26.93659721926097</v>
       </c>
       <c r="F37">
-        <v>1.826469624287331</v>
+        <v>2.279555115657354</v>
       </c>
       <c r="G37">
-        <v>-5.784351844159915</v>
+        <v>-8.22654128848027</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-16.67049037573472</v>
       </c>
       <c r="E38">
-        <v>-25.3245012287964</v>
+        <v>-27.46197718820887</v>
       </c>
       <c r="F38">
-        <v>2.080606116526996</v>
+        <v>2.34256239704909</v>
       </c>
       <c r="G38">
-        <v>-6.607479265953225</v>
+        <v>-8.108907673833347</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-16.38380606696163</v>
       </c>
       <c r="E39">
-        <v>-23.36633925466565</v>
+        <v>-25.98896421994187</v>
       </c>
       <c r="F39">
-        <v>2.005700165761449</v>
+        <v>1.976549916856934</v>
       </c>
       <c r="G39">
-        <v>-6.191426455305319</v>
+        <v>-7.520471446410051</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-16.13790008666793</v>
       </c>
       <c r="E40">
-        <v>-23.75297583696654</v>
+        <v>-26.22329463594278</v>
       </c>
       <c r="F40">
-        <v>2.091512401752255</v>
+        <v>2.015123673335696</v>
       </c>
       <c r="G40">
-        <v>-7.015944306225122</v>
+        <v>-7.964680446869458</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-15.9470101894087</v>
       </c>
       <c r="E41">
-        <v>-23.60755747963223</v>
+        <v>-26.37518418263405</v>
       </c>
       <c r="F41">
-        <v>1.600658327018991</v>
+        <v>2.392387039592674</v>
       </c>
       <c r="G41">
-        <v>-5.385755540140586</v>
+        <v>-8.310857572819968</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-15.80670618367684</v>
       </c>
       <c r="E42">
-        <v>-23.07181636215478</v>
+        <v>-24.92971792175571</v>
       </c>
       <c r="F42">
-        <v>2.35126191151329</v>
+        <v>2.022045511353488</v>
       </c>
       <c r="G42">
-        <v>-6.977442661603398</v>
+        <v>-7.750084263922822</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-15.70066460186467</v>
       </c>
       <c r="E43">
-        <v>-22.26946586594976</v>
+        <v>-25.16830057484982</v>
       </c>
       <c r="F43">
-        <v>2.228149948109228</v>
+        <v>2.230651617665682</v>
       </c>
       <c r="G43">
-        <v>-5.747806731951901</v>
+        <v>-7.840568094602181</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-15.60665902521169</v>
       </c>
       <c r="E44">
-        <v>-20.23933738288911</v>
+        <v>-23.86992820668863</v>
       </c>
       <c r="F44">
-        <v>1.620249216095199</v>
+        <v>1.90526393164162</v>
       </c>
       <c r="G44">
-        <v>-6.517091441094504</v>
+        <v>-7.836618613773831</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-15.53467866197953</v>
       </c>
       <c r="E45">
-        <v>-21.65235712750249</v>
+        <v>-23.50663590789728</v>
       </c>
       <c r="F45">
-        <v>2.231847780195324</v>
+        <v>2.180018488536965</v>
       </c>
       <c r="G45">
-        <v>-6.879616040917934</v>
+        <v>-7.366749574839532</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-15.47901909091018</v>
       </c>
       <c r="E46">
-        <v>-20.4286094825137</v>
+        <v>-23.03811998706371</v>
       </c>
       <c r="F46">
-        <v>2.174418724894041</v>
+        <v>2.113131134230516</v>
       </c>
       <c r="G46">
-        <v>-6.867247842783217</v>
+        <v>-7.881880392386747</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-15.42635611233976</v>
       </c>
       <c r="E47">
-        <v>-19.50393131793948</v>
+        <v>-22.5611403483098</v>
       </c>
       <c r="F47">
-        <v>2.213131647096473</v>
+        <v>2.227359685606957</v>
       </c>
       <c r="G47">
-        <v>-7.207105137299258</v>
+        <v>-7.911993114611958</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-15.3662915718039</v>
       </c>
       <c r="E48">
-        <v>-20.30260016477627</v>
+        <v>-22.90982831842641</v>
       </c>
       <c r="F48">
-        <v>2.077638904490169</v>
+        <v>2.352411685468376</v>
       </c>
       <c r="G48">
-        <v>-7.48876635178045</v>
+        <v>-7.56776258943854</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-15.3177280520388</v>
       </c>
       <c r="E49">
-        <v>-21.05573520546593</v>
+        <v>-22.63039882978311</v>
       </c>
       <c r="F49">
-        <v>1.71352835585484</v>
+        <v>2.360042605982965</v>
       </c>
       <c r="G49">
-        <v>-7.574919988894444</v>
+        <v>-8.329542291843614</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-15.28469328200926</v>
       </c>
       <c r="E50">
-        <v>-17.74120016808375</v>
+        <v>-22.0745467592376</v>
       </c>
       <c r="F50">
-        <v>2.082564377067214</v>
+        <v>2.023213509391435</v>
       </c>
       <c r="G50">
-        <v>-7.530234245205361</v>
+        <v>-8.169689289934366</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-15.26141619265471</v>
       </c>
       <c r="E51">
-        <v>-17.1284070653658</v>
+        <v>-21.24345403850589</v>
       </c>
       <c r="F51">
-        <v>1.697643582538757</v>
+        <v>2.015059060678277</v>
       </c>
       <c r="G51">
-        <v>-7.2097303999119</v>
+        <v>-9.178793228487313</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-15.25239384305418</v>
       </c>
       <c r="E52">
-        <v>-17.76448105295719</v>
+        <v>-20.7809519311545</v>
       </c>
       <c r="F52">
-        <v>2.441847200479027</v>
+        <v>1.949227046442995</v>
       </c>
       <c r="G52">
-        <v>-8.610091163023611</v>
+        <v>-8.345893076262074</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-15.27928046815216</v>
       </c>
       <c r="E53">
-        <v>-17.88106661628466</v>
+        <v>-20.29972911225541</v>
       </c>
       <c r="F53">
-        <v>1.778614839427603</v>
+        <v>2.23292631455377</v>
       </c>
       <c r="G53">
-        <v>-6.965729951485456</v>
+        <v>-8.965915218675558</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-15.34859225145625</v>
       </c>
       <c r="E54">
-        <v>-18.03071456834213</v>
+        <v>-20.63958202958305</v>
       </c>
       <c r="F54">
-        <v>2.153268848365764</v>
+        <v>2.116608620587469</v>
       </c>
       <c r="G54">
-        <v>-8.632046701040059</v>
+        <v>-9.397984448642458</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-15.44949798171612</v>
       </c>
       <c r="E55">
-        <v>-16.57064850726307</v>
+        <v>-19.69889570939171</v>
       </c>
       <c r="F55">
-        <v>1.663693772902422</v>
+        <v>2.372362085997399</v>
       </c>
       <c r="G55">
-        <v>-9.19707075040963</v>
+        <v>-9.471246821426529</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-15.58703319218463</v>
       </c>
       <c r="E56">
-        <v>-16.66146705348689</v>
+        <v>-20.09847467040652</v>
       </c>
       <c r="F56">
-        <v>2.164940545071209</v>
+        <v>1.855977727909855</v>
       </c>
       <c r="G56">
-        <v>-8.177025458849391</v>
+        <v>-9.506034033953192</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-15.7720129019773</v>
       </c>
       <c r="E57">
-        <v>-17.29493716852387</v>
+        <v>-19.80718057986313</v>
       </c>
       <c r="F57">
-        <v>2.364868674471675</v>
+        <v>2.187415809443965</v>
       </c>
       <c r="G57">
-        <v>-8.440134376128508</v>
+        <v>-9.989751084878261</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-16.00094170890994</v>
       </c>
       <c r="E58">
-        <v>-15.26518454880586</v>
+        <v>-19.24615699200086</v>
       </c>
       <c r="F58">
-        <v>2.269540153757508</v>
+        <v>2.279780431590915</v>
       </c>
       <c r="G58">
-        <v>-8.97535027346248</v>
+        <v>-9.774052490267048</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-16.24955808743456</v>
       </c>
       <c r="E59">
-        <v>-15.98705953342058</v>
+        <v>-18.85265524310434</v>
       </c>
       <c r="F59">
-        <v>1.534311068259167</v>
+        <v>2.335103776954283</v>
       </c>
       <c r="G59">
-        <v>-8.252552244782324</v>
+        <v>-9.212117179885617</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.51918375124766</v>
       </c>
       <c r="E60">
-        <v>-15.2509198556817</v>
+        <v>-19.19023939495414</v>
       </c>
       <c r="F60">
-        <v>2.080929179814088</v>
+        <v>2.235149652662884</v>
       </c>
       <c r="G60">
-        <v>-8.876666221482346</v>
+        <v>-9.845854912468299</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.80930258603099</v>
       </c>
       <c r="E61">
-        <v>-15.83201364034596</v>
+        <v>-19.73763680452733</v>
       </c>
       <c r="F61">
-        <v>2.480787095349827</v>
+        <v>2.179521468095285</v>
       </c>
       <c r="G61">
-        <v>-8.654727248529605</v>
+        <v>-9.607538670732785</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-17.10851080911189</v>
       </c>
       <c r="E62">
-        <v>-14.23999237515739</v>
+        <v>-18.86250467407103</v>
       </c>
       <c r="F62">
-        <v>2.064032141531784</v>
+        <v>2.254087788225686</v>
       </c>
       <c r="G62">
-        <v>-8.850807550275098</v>
+        <v>-9.660053854622245</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-17.38807560066465</v>
       </c>
       <c r="E63">
-        <v>-16.21933402222201</v>
+        <v>-18.69563040688837</v>
       </c>
       <c r="F63">
-        <v>1.777229809130122</v>
+        <v>2.428795443680518</v>
       </c>
       <c r="G63">
-        <v>-7.360181452489618</v>
+        <v>-9.382070656235182</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-17.65132384389018</v>
       </c>
       <c r="E64">
-        <v>-15.99361676378369</v>
+        <v>-17.09944294561274</v>
       </c>
       <c r="F64">
-        <v>2.180732541238178</v>
+        <v>2.143996103658826</v>
       </c>
       <c r="G64">
-        <v>-9.037267406683469</v>
+        <v>-9.885101429836361</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.89705451243254</v>
       </c>
       <c r="E65">
-        <v>-15.36049081277129</v>
+        <v>-18.85101593551357</v>
       </c>
       <c r="F65">
-        <v>2.433250403572774</v>
+        <v>1.794486358865242</v>
       </c>
       <c r="G65">
-        <v>-8.644540699905267</v>
+        <v>-10.56186632279295</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-18.11571776807449</v>
       </c>
       <c r="E66">
-        <v>-15.14091416508737</v>
+        <v>-19.58442494342582</v>
       </c>
       <c r="F66">
-        <v>2.344731062909619</v>
+        <v>1.968695337143589</v>
       </c>
       <c r="G66">
-        <v>-9.816725422268252</v>
+        <v>-9.753748914474697</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.28506662323334</v>
       </c>
       <c r="E67">
-        <v>-14.76655880429529</v>
+        <v>-18.27252149492971</v>
       </c>
       <c r="F67">
-        <v>2.10430570792109</v>
+        <v>2.036752346222791</v>
       </c>
       <c r="G67">
-        <v>-9.161611497138496</v>
+        <v>-9.931651010664051</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.41570824997902</v>
       </c>
       <c r="E68">
-        <v>-14.14161580581476</v>
+        <v>-18.98101483885176</v>
       </c>
       <c r="F68">
-        <v>2.169902465813978</v>
+        <v>2.256745190853866</v>
       </c>
       <c r="G68">
-        <v>-8.780660400843482</v>
+        <v>-10.07754675257973</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.51087383416597</v>
       </c>
       <c r="E69">
-        <v>-14.31648735809495</v>
+        <v>-17.56194052449012</v>
       </c>
       <c r="F69">
-        <v>2.402797961111059</v>
+        <v>2.255572222611502</v>
       </c>
       <c r="G69">
-        <v>-9.029517419576036</v>
+        <v>-9.564339361990836</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.5653353300563</v>
       </c>
       <c r="E70">
-        <v>-15.45755865312571</v>
+        <v>-18.96120729354221</v>
       </c>
       <c r="F70">
-        <v>2.298571117756019</v>
+        <v>1.884963960068615</v>
       </c>
       <c r="G70">
-        <v>-9.156927075200427</v>
+        <v>-9.822542050780752</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.56448611188106</v>
       </c>
       <c r="E71">
-        <v>-16.26028048419936</v>
+        <v>-17.68730227044446</v>
       </c>
       <c r="F71">
-        <v>2.357945179719076</v>
+        <v>2.275565698245472</v>
       </c>
       <c r="G71">
-        <v>-7.415967455371877</v>
+        <v>-10.53841772873829</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.52613808300531</v>
       </c>
       <c r="E72">
-        <v>-13.15844334248345</v>
+        <v>-18.62903466813157</v>
       </c>
       <c r="F72">
-        <v>1.953799634506448</v>
+        <v>1.802065920600857</v>
       </c>
       <c r="G72">
-        <v>-8.763789860775356</v>
+        <v>-10.53775893017598</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.45750702227907</v>
       </c>
       <c r="E73">
-        <v>-16.47411502684156</v>
+        <v>-19.92531940977523</v>
       </c>
       <c r="F73">
-        <v>1.822910957924904</v>
+        <v>2.026651234113054</v>
       </c>
       <c r="G73">
-        <v>-8.777932511319122</v>
+        <v>-9.967381728669405</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.35673813540933</v>
       </c>
       <c r="E74">
-        <v>-15.80861954362234</v>
+        <v>-19.14905292385438</v>
       </c>
       <c r="F74">
-        <v>2.380791552688287</v>
+        <v>1.899520032070608</v>
       </c>
       <c r="G74">
-        <v>-9.454571603545221</v>
+        <v>-9.8548496646985</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.21497659087081</v>
       </c>
       <c r="E75">
-        <v>-14.76155936899082</v>
+        <v>-18.47954068419036</v>
       </c>
       <c r="F75">
-        <v>2.606036246653112</v>
+        <v>1.602527123879707</v>
       </c>
       <c r="G75">
-        <v>-7.698741013154264</v>
+        <v>-10.09314273261524</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.05506606698087</v>
       </c>
       <c r="E76">
-        <v>-15.64968369137513</v>
+        <v>-18.83218201211567</v>
       </c>
       <c r="F76">
-        <v>1.970910391578675</v>
+        <v>2.246145401567644</v>
       </c>
       <c r="G76">
-        <v>-8.386682307851435</v>
+        <v>-9.799083525089477</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.8844707352692</v>
       </c>
       <c r="E77">
-        <v>-16.50476373892547</v>
+        <v>-20.38694299316913</v>
       </c>
       <c r="F77">
-        <v>1.507886148109863</v>
+        <v>1.962777480417989</v>
       </c>
       <c r="G77">
-        <v>-8.015801891086884</v>
+        <v>-9.483717646472964</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.70003831396386</v>
       </c>
       <c r="E78">
-        <v>-15.09761742510004</v>
+        <v>-19.95669720617438</v>
       </c>
       <c r="F78">
-        <v>1.787451862880668</v>
+        <v>1.794774630721416</v>
       </c>
       <c r="G78">
-        <v>-8.846497219982968</v>
+        <v>-9.481963057337151</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.49368466745803</v>
       </c>
       <c r="E79">
-        <v>-16.84045046016606</v>
+        <v>-20.34977327851417</v>
       </c>
       <c r="F79">
-        <v>1.545619940042186</v>
+        <v>1.934077863380598</v>
       </c>
       <c r="G79">
-        <v>-8.17925676654286</v>
+        <v>-9.46270561393521</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.28818576881849</v>
       </c>
       <c r="E80">
-        <v>-17.06326043829145</v>
+        <v>-20.72212705379487</v>
       </c>
       <c r="F80">
-        <v>1.934617958927223</v>
+        <v>1.694568682739565</v>
       </c>
       <c r="G80">
-        <v>-7.717127783079377</v>
+        <v>-8.977776903342766</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.08810512762726</v>
       </c>
       <c r="E81">
-        <v>-16.27790530503722</v>
+        <v>-21.46471527852067</v>
       </c>
       <c r="F81">
-        <v>1.807990404265679</v>
+        <v>1.703604514369302</v>
       </c>
       <c r="G81">
-        <v>-8.066751186936267</v>
+        <v>-8.462632843613395</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-16.88736974552019</v>
       </c>
       <c r="E82">
-        <v>-17.07997956432778</v>
+        <v>-21.48122156627862</v>
       </c>
       <c r="F82">
-        <v>2.056300160194053</v>
+        <v>1.725657311366631</v>
       </c>
       <c r="G82">
-        <v>-7.848400845348097</v>
+        <v>-8.949607471349108</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-16.68356753797099</v>
       </c>
       <c r="E83">
-        <v>-18.97325303440261</v>
+        <v>-23.8160076666793</v>
       </c>
       <c r="F83">
-        <v>1.972121464721568</v>
+        <v>1.554233304296496</v>
       </c>
       <c r="G83">
-        <v>-7.315661236077499</v>
+        <v>-7.737365147960942</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.5001269983925</v>
       </c>
       <c r="E84">
-        <v>-19.25429013131863</v>
+        <v>-23.36871670351968</v>
       </c>
       <c r="F84">
-        <v>1.754872172928564</v>
+        <v>1.810861525683782</v>
       </c>
       <c r="G84">
-        <v>-6.814825354168858</v>
+        <v>-8.721166586957239</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.34343727038525</v>
       </c>
       <c r="E85">
-        <v>-19.62069802022726</v>
+        <v>-23.9105259761674</v>
       </c>
       <c r="F85">
-        <v>1.617938071041389</v>
+        <v>1.907585017104264</v>
       </c>
       <c r="G85">
-        <v>-6.794634336924843</v>
+        <v>-8.482790755402018</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-16.20655837835457</v>
       </c>
       <c r="E86">
-        <v>-22.95773051647955</v>
+        <v>-25.09456343258293</v>
       </c>
       <c r="F86">
-        <v>1.294038132872754</v>
+        <v>1.753394365481969</v>
       </c>
       <c r="G86">
-        <v>-6.903240093886174</v>
+        <v>-8.624627768486551</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-16.09472905224759</v>
       </c>
       <c r="E87">
-        <v>-22.29695370317632</v>
+        <v>-24.79510903187771</v>
       </c>
       <c r="F87">
-        <v>1.703877875612226</v>
+        <v>1.911339178173751</v>
       </c>
       <c r="G87">
-        <v>-6.409561611433436</v>
+        <v>-7.919590816624585</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-16.02903851023737</v>
       </c>
       <c r="E88">
-        <v>-24.35920718084737</v>
+        <v>-26.13688229492841</v>
       </c>
       <c r="F88">
-        <v>1.884289669002736</v>
+        <v>1.31008360946498</v>
       </c>
       <c r="G88">
-        <v>-6.672975098902166</v>
+        <v>-8.093599711259758</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-16.01526311287127</v>
       </c>
       <c r="E89">
-        <v>-25.35497785886802</v>
+        <v>-27.47491956692279</v>
       </c>
       <c r="F89">
-        <v>1.702913655955367</v>
+        <v>1.655151648244754</v>
       </c>
       <c r="G89">
-        <v>-7.107169699105278</v>
+        <v>-8.292374797074217</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-16.04127167692047</v>
       </c>
       <c r="E90">
-        <v>-27.26084501515819</v>
+        <v>-28.21826857528188</v>
       </c>
       <c r="F90">
-        <v>1.959540220607849</v>
+        <v>1.7649434638118</v>
       </c>
       <c r="G90">
-        <v>-6.66541712343601</v>
+        <v>-8.289031146079553</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-16.11638103662379</v>
       </c>
       <c r="E91">
-        <v>-27.15609235441276</v>
+        <v>-30.00148201307429</v>
       </c>
       <c r="F91">
-        <v>1.492413901760374</v>
+        <v>1.868459567935238</v>
       </c>
       <c r="G91">
-        <v>-6.845626669866237</v>
+        <v>-7.454095008347664</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.25494669000906</v>
       </c>
       <c r="E92">
-        <v>-29.79772332509917</v>
+        <v>-32.40203966996238</v>
       </c>
       <c r="F92">
-        <v>2.179649036675317</v>
+        <v>1.616468547268822</v>
       </c>
       <c r="G92">
-        <v>-6.320431793879638</v>
+        <v>-7.846030494741979</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-16.4577141865904</v>
       </c>
       <c r="E93">
-        <v>-30.99921352034026</v>
+        <v>-33.56554955370113</v>
       </c>
       <c r="F93">
-        <v>2.055708705868454</v>
+        <v>1.560111399386761</v>
       </c>
       <c r="G93">
-        <v>-6.29444070085082</v>
+        <v>-7.87610017987518</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-16.70304660836699</v>
       </c>
       <c r="E94">
-        <v>-32.70522326901291</v>
+        <v>-34.49741440652554</v>
       </c>
       <c r="F94">
-        <v>1.722607262589523</v>
+        <v>0.9178599279134424</v>
       </c>
       <c r="G94">
-        <v>-6.317919089815331</v>
+        <v>-7.222151566775246</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-16.9993388573147</v>
       </c>
       <c r="E95">
-        <v>-36.38188905160347</v>
+        <v>-36.61266008703435</v>
       </c>
       <c r="F95">
-        <v>1.386015079075194</v>
+        <v>1.025799513967829</v>
       </c>
       <c r="G95">
-        <v>-6.513986149378668</v>
+        <v>-7.773496441976548</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.35342761794974</v>
       </c>
       <c r="E96">
-        <v>-38.20444587157453</v>
+        <v>-37.62776282059374</v>
       </c>
       <c r="F96">
-        <v>1.217198772589072</v>
+        <v>1.115886125757081</v>
       </c>
       <c r="G96">
-        <v>-6.148528406207443</v>
+        <v>-7.380826014472514</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.75170432712305</v>
       </c>
       <c r="E97">
-        <v>-39.09481178859264</v>
+        <v>-40.34642539838762</v>
       </c>
       <c r="F97">
-        <v>1.479673611105317</v>
+        <v>0.5083954356074384</v>
       </c>
       <c r="G97">
-        <v>-8.023776995290989</v>
+        <v>-7.468502502534571</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.17572223167789</v>
       </c>
       <c r="E98">
-        <v>-41.60928320914366</v>
+        <v>-42.70451729026878</v>
       </c>
       <c r="F98">
-        <v>0.4375078951128707</v>
+        <v>1.040252868411875</v>
       </c>
       <c r="G98">
-        <v>-6.0873991828248</v>
+        <v>-7.891719333729461</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.61644910608251</v>
       </c>
       <c r="E99">
-        <v>-44.72223322607439</v>
+        <v>-43.4584538708578</v>
       </c>
       <c r="F99">
-        <v>0.6712383847519736</v>
+        <v>0.8191814894223541</v>
       </c>
       <c r="G99">
-        <v>-6.503865811665115</v>
+        <v>-7.464615922071467</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-19.09362495404912</v>
       </c>
       <c r="E100">
-        <v>-46.04087504389392</v>
+        <v>-45.18290356568968</v>
       </c>
       <c r="F100">
-        <v>0.8424470162973811</v>
+        <v>0.3432902150858578</v>
       </c>
       <c r="G100">
-        <v>-6.504259766584289</v>
+        <v>-7.856650724831961</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-19.55945505853982</v>
       </c>
       <c r="E101">
-        <v>-49.08052831265501</v>
+        <v>-48.24706153942477</v>
       </c>
       <c r="F101">
-        <v>0.7441827615076925</v>
+        <v>0.1859559091699393</v>
       </c>
       <c r="G101">
-        <v>-6.834331088486244</v>
+        <v>-7.630686128503467</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-20.04790797634749</v>
       </c>
       <c r="E102">
-        <v>-49.79144891864517</v>
+        <v>-49.84822579363483</v>
       </c>
       <c r="F102">
-        <v>0.378437015619238</v>
+        <v>0.01665666448798471</v>
       </c>
       <c r="G102">
-        <v>-6.291143397493706</v>
+        <v>-7.82149935229598</v>
       </c>
     </row>
   </sheetData>
